--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N58_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N58_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>98.07086212684791</v>
+        <v>15.93651509561279</v>
       </c>
       <c r="D2" t="n">
-        <v>97.76738260251669</v>
+        <v>15.88719967290896</v>
       </c>
       <c r="E2" t="n">
-        <v>23.66773302234828</v>
+        <v>3.846006616131596</v>
       </c>
       <c r="F2" t="n">
-        <v>23.84947455960042</v>
+        <v>3.875539615935069</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.89130829066708</v>
+        <v>8.594837597233401</v>
       </c>
       <c r="D3" t="n">
-        <v>52.76415072532208</v>
+        <v>8.574174492864838</v>
       </c>
       <c r="E3" t="n">
-        <v>23.66773302234828</v>
+        <v>3.846006616131596</v>
       </c>
       <c r="F3" t="n">
-        <v>23.84947455960042</v>
+        <v>3.875539615935069</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.01947248388391</v>
+        <v>7.153164278631135</v>
       </c>
       <c r="D4" t="n">
-        <v>43.00711966941238</v>
+        <v>6.988656946279511</v>
       </c>
       <c r="E4" t="n">
-        <v>23.66773302234828</v>
+        <v>3.846006616131596</v>
       </c>
       <c r="F4" t="n">
-        <v>23.84947455960042</v>
+        <v>3.875539615935069</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
